--- a/docs/THIET_KE_CODE_VA_ENDPOINT.xlsx
+++ b/docs/THIET_KE_CODE_VA_ENDPOINT.xlsx
@@ -36,7 +36,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'00_BIA'!$A$5:$B$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_MUC_LUC'!$A$4:$C$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_QUY_UOC'!$A$4:$C$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'03_OBJECT_CATALOG'!$A$4:$H$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'03_OBJECT_CATALOG'!$A$4:$H$95</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_ENTITY_CATALOG'!$A$4:$H$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'E_Order'!$A$4:$F$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'E_OrderItem'!$A$4:$F$18</definedName>
@@ -47,7 +47,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'E_Chat'!$A$4:$F$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'E_Production'!$A$4:$F$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'E_ChangeReceipt'!$A$4:$F$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'05_DTO_CATALOG'!$A$4:$F$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'05_DTO_CATALOG'!$A$4:$F$38</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'06_SERVICE_CATALOG'!$A$4:$H$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'07_REPOSITORY'!$A$4:$H$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'08_CONTROLLER'!$A$4:$H$19</definedName>
@@ -55,8 +55,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'10_CAMUNDA_EVENT'!$A$16:$F$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'11_WF_MAPPING'!$A$4:$G$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'12_KE_HOACH'!$A$4:$E$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'13_QUYET_DINH'!$A$4:$E$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'14_KIEM_THU'!$A$4:$D$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'13_QUYET_DINH'!$A$4:$E$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'14_KIEM_THU'!$A$4:$D$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -389,8 +389,8 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="T_05_DTO_CATALOG" displayName="T_05_DTO_CATALOG" ref="A4:F37" headerRowCount="1">
-  <autoFilter ref="A4:F37"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="T_05_DTO_CATALOG" displayName="T_05_DTO_CATALOG" ref="A4:F38" headerRowCount="1">
+  <autoFilter ref="A4:F38"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Tên file"/>
     <tableColumn id="2" name="Loại"/>
@@ -547,8 +547,8 @@
 </file>
 
 <file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="24" name="T_13_QUYET_DINH" displayName="T_13_QUYET_DINH" ref="A4:E12" headerRowCount="1">
-  <autoFilter ref="A4:E12"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="24" name="T_13_QUYET_DINH" displayName="T_13_QUYET_DINH" ref="A4:E13" headerRowCount="1">
+  <autoFilter ref="A4:E13"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Mã"/>
     <tableColumn id="2" name="Chủ đề"/>
@@ -561,8 +561,8 @@
 </file>
 
 <file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="25" name="T_14_KIEM_THU" displayName="T_14_KIEM_THU" ref="A4:D17" headerRowCount="1">
-  <autoFilter ref="A4:D17"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="25" name="T_14_KIEM_THU" displayName="T_14_KIEM_THU" ref="A4:D20" headerRowCount="1">
+  <autoFilter ref="A4:D20"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Mã"/>
     <tableColumn id="2" name="Nhóm"/>
@@ -586,8 +586,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T_03_OBJECT_CATALOG" displayName="T_03_OBJECT_CATALOG" ref="A4:H94" headerRowCount="1">
-  <autoFilter ref="A4:H94"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T_03_OBJECT_CATALOG" displayName="T_03_OBJECT_CATALOG" ref="A4:H95" headerRowCount="1">
+  <autoFilter ref="A4:H95"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Loại"/>
     <tableColumn id="2" name="Tên file"/>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
     </row>
@@ -3087,7 +3087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3251,9 +3251,9 @@
           <t>Request</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>TẠO MỚI</t>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>SỬA</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>name, description, quantity, images/spec</t>
+          <t>description &lt;= 4.000 từ, imageUrls: string[], quantity</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Tạo draft.</t>
+          <t>Tạo draft; imageUrls có thể rỗng, mỗi URL dùng HTTP/HTTPS.</t>
         </is>
       </c>
     </row>
@@ -3283,9 +3283,9 @@
           <t>Request</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>TẠO MỚI</t>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>SỬA</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>version và trường draft</t>
+          <t>expectedVersion, description, imageUrls, quantity</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Chỉ draft owner.</t>
+          <t>Chỉ draft owner; cùng validation create.</t>
         </is>
       </c>
     </row>
@@ -3371,12 +3371,12 @@
     <row r="12" ht="42" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>ReviewOrderRequest.java</t>
+          <t>CustomRequestSubmissionDTO.java</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Request</t>
+          <t>Response</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
@@ -3386,24 +3386,24 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>05</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>decision, reason, optional staffId, expectedVersion</t>
+          <t>draftId, orderId, version, orderType, status, message</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Manager review.</t>
+          <t>Không trả giá custom chưa thỏa thuận.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="42" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>AssignOrderRequest.java</t>
+          <t>ReviewOrderRequest.java</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -3423,24 +3423,24 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>staffId, expectedVersion</t>
+          <t>decision, reason, optional staffId, expectedVersion</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Manager assign.</t>
+          <t>Manager review.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>OrderAssignmentDTO.java</t>
+          <t>AssignOrderRequest.java</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Response</t>
+          <t>Request</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
@@ -3455,19 +3455,19 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>orderId, staffId, source, status, timestamps</t>
+          <t>staffId, expectedVersion</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Assignment cấp Order.</t>
+          <t>Manager assign.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>ChatThreadDTO.java</t>
+          <t>OrderAssignmentDTO.java</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -3482,29 +3482,29 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>07</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>threadId, orderId, peer, createdAt</t>
+          <t>orderId, staffId, source, status, timestamps</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Không chứa manager member.</t>
+          <t>Assignment cấp Order.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>SendOrderMessageRequest.java</t>
+          <t>ChatThreadDTO.java</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Request</t>
+          <t>Response</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
@@ -3519,24 +3519,24 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>clientMessageId, content, attachments</t>
+          <t>threadId, orderId, peer, createdAt</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Idempotent theo clientMessageId.</t>
+          <t>Không chứa manager member.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="42" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>OrderChatMessageDTO.java</t>
+          <t>SendOrderMessageRequest.java</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Response</t>
+          <t>Request</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
@@ -3551,24 +3551,24 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>messageId, sender, content, sentAt</t>
+          <t>clientMessageId, content, attachments</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Cho member hợp lệ.</t>
+          <t>Idempotent theo clientMessageId.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="42" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>SubmitAgreementRequest.java</t>
+          <t>OrderChatMessageDTO.java</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Request</t>
+          <t>Response</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
@@ -3583,19 +3583,19 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>spec, amount/deadline, voucherId, expectedVersion</t>
+          <t>messageId, sender, content, sentAt</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Catalog price read-only; custom amount USER nhập theo trao đổi.</t>
+          <t>Cho member hợp lệ.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="42" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>ReviewAgreementRequest.java</t>
+          <t>SubmitAgreementRequest.java</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -3615,24 +3615,24 @@
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>agreementVersion, decision, reason, expectedOrderVersion</t>
+          <t>spec, amount/deadline, voucherId, expectedVersion</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Staff phụ trách.</t>
+          <t>Catalog price read-only; custom amount USER nhập theo trao đổi.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="42" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>OrderAgreementDTO.java</t>
+          <t>ReviewAgreementRequest.java</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Response</t>
+          <t>Request</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
@@ -3647,24 +3647,24 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>version, snapshot, totals, status, timestamps</t>
+          <t>agreementVersion, decision, reason, expectedOrderVersion</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Giá custom null trước chốt.</t>
+          <t>Staff phụ trách.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="42" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>CreatePaymentAttemptRequest.java</t>
+          <t>OrderAgreementDTO.java</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Request</t>
+          <t>Response</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
@@ -3674,29 +3674,29 @@
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>08</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>expectedOrderVersion</t>
+          <t>version, snapshot, totals, status, timestamps</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>ONLINE + ORDER_ACCEPTED.</t>
+          <t>Giá custom null trước chốt.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="42" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>PaymentAttemptDTO.java</t>
+          <t>CreatePaymentAttemptRequest.java</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Response</t>
+          <t>Request</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
@@ -3711,24 +3711,24 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>attemptId, status, amount, dueAt, payUrl</t>
+          <t>expectedOrderVersion</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Không trả provider secret/result raw.</t>
+          <t>ONLINE + ORDER_ACCEPTED.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="42" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>MomoWebhookRequest.java</t>
+          <t>PaymentAttemptDTO.java</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Request</t>
+          <t>Response</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
@@ -3743,19 +3743,19 @@
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>provider fields/signature</t>
+          <t>attemptId, status, amount, dueAt, payUrl</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>Validate chữ ký và số tiền.</t>
+          <t>Không trả provider secret/result raw.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="42" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>StartProductionRequest.java</t>
+          <t>MomoWebhookRequest.java</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -3775,19 +3775,19 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>expectedVersion, plannedStartReason?</t>
+          <t>provider fields/signature</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>Staff bấm bắt đầu.</t>
+          <t>Validate chữ ký và số tiền.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="42" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>SubmitCheckpointRequest.java</t>
+          <t>StartProductionRequest.java</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -3802,24 +3802,24 @@
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>09</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>orderItemId, type, attempt, images, note</t>
+          <t>expectedVersion, plannedStartReason?</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>Checkpoint theo loại, không theo từng chiếc.</t>
+          <t>Staff bấm bắt đầu.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="42" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>ReviewCheckpointRequest.java</t>
+          <t>SubmitCheckpointRequest.java</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
@@ -3839,19 +3839,19 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>decision, reason, expectedCheckpointVersion</t>
+          <t>orderItemId, type, attempt, images, note</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>Chỉ checkpoint 2 qua manager.</t>
+          <t>Checkpoint theo loại, không theo từng chiếc.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="42" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>CreateChangeRequest.java</t>
+          <t>ReviewCheckpointRequest.java</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -3866,24 +3866,24 @@
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>orderItemId, requestedChanges, expectedVersion</t>
+          <t>decision, reason, expectedCheckpointVersion</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>Không có price/deadline change.</t>
+          <t>Chỉ checkpoint 2 qua manager.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="42" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>ReviewChangeRequest.java</t>
+          <t>CreateChangeRequest.java</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -3903,24 +3903,24 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>decision, reason, expectedVersion</t>
+          <t>orderItemId, requestedChanges, expectedVersion</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Staff phụ trách.</t>
+          <t>Không có price/deadline change.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="42" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>ChangeRequestDTO.java</t>
+          <t>ReviewChangeRequest.java</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Response</t>
+          <t>Request</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
@@ -3935,24 +3935,24 @@
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>request, decision, timestamps</t>
+          <t>decision, reason, expectedVersion</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>Không phát sinh payment.</t>
+          <t>Staff phụ trách.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="42" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>ShipOrderRequest.java</t>
+          <t>ChangeRequestDTO.java</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Request</t>
+          <t>Response</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
@@ -3962,24 +3962,24 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>items[orderItemId, exportedQuantity], note, expectedVersion</t>
+          <t>request, decision, timestamps</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Một snapshot bàn giao.</t>
+          <t>Không phát sinh payment.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="42" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>ReceiptConfirmRequest.java</t>
+          <t>ShipOrderRequest.java</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -3987,9 +3987,9 @@
           <t>Request</t>
         </is>
       </c>
-      <c r="C31" s="10" t="inlineStr">
-        <is>
-          <t>SỬA</t>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>TẠO MỚI</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
@@ -3999,29 +3999,29 @@
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>items[orderItemId, receivedQuantity], acceptMismatch, expectedVersion</t>
+          <t>items[orderItemId, exportedQuantity], note, expectedVersion</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>USER/Guest dùng cùng nghiệp vụ.</t>
+          <t>Một snapshot bàn giao.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="42" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>OrderReceiptDTO.java</t>
+          <t>ReceiptConfirmRequest.java</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Response</t>
-        </is>
-      </c>
-      <c r="C32" s="11" t="inlineStr">
-        <is>
-          <t>TẠO MỚI</t>
+          <t>Request</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>SỬA</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>items snapshot, mismatch, confirmedAt</t>
+          <t>items[orderItemId, receivedQuantity], acceptMismatch, expectedVersion</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>Kết quả nhận hàng.</t>
+          <t>USER/Guest dùng cùng nghiệp vụ.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="42" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>CancelOrderRequest.java</t>
+          <t>OrderReceiptDTO.java</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>Request</t>
+          <t>Response</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
@@ -4058,24 +4058,24 @@
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>reason, expectedVersion</t>
+          <t>items snapshot, mismatch, confirmedAt</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>Chỉ trước ORDER_ACCEPTED cho USER/Guest.</t>
+          <t>Kết quả nhận hàng.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="42" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>ReorderRequest.java</t>
+          <t>CancelOrderRequest.java</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -4090,29 +4090,29 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>06</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>expectedSourceOrderVersion</t>
+          <t>reason, expectedVersion</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Catalog thêm giỏ; custom tạo draft.</t>
+          <t>Chỉ trước ORDER_ACCEPTED cho USER/Guest.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="42" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>OrderActionResponse.java</t>
+          <t>ReorderRequest.java</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>Response</t>
+          <t>Request</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
@@ -4122,24 +4122,24 @@
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>06-12</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>orderId, status, paymentStatus, version, message</t>
+          <t>expectedSourceOrderVersion</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>Response chung cho command.</t>
+          <t>Catalog thêm giỏ; custom tạo draft.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="42" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>OrderDTO.java</t>
+          <t>OrderActionResponse.java</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
@@ -4147,61 +4147,93 @@
           <t>Response</t>
         </is>
       </c>
-      <c r="C36" s="10" t="inlineStr">
-        <is>
-          <t>SỬA</t>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>TẠO MỚI</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>04-12</t>
+          <t>06-12</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>Lifecycle, payment, snapshots, assigned staff, deadlines</t>
+          <t>orderId, status, paymentStatus, version, message</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Giá custom chưa chốt là null.</t>
+          <t>Response chung cho command.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="42" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
+          <t>OrderDTO.java</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Response</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>SỬA</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>04-12</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>Lifecycle, payment, snapshots, assigned staff, deadlines</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>Giá custom chưa chốt là null.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="42" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
           <t>OrderItemDTO.java</t>
         </is>
       </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>Response</t>
         </is>
       </c>
-      <c r="C37" s="10" t="inlineStr">
+      <c r="C38" s="10" t="inlineStr">
         <is>
           <t>SỬA</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>04-12</t>
         </is>
       </c>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>sourceType, names/spec/price/duration/completion</t>
         </is>
       </c>
-      <c r="F37" s="6" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>Dữ liệu snapshot.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F37"/>
+  <autoFilter ref="A4:F38"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
@@ -7757,7 +7789,7 @@
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>CheckoutResponseDTO</t>
+          <t>CustomRequestSubmissionDTO</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
@@ -11023,7 +11055,7 @@
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thứ tự dependency đã thống nhất; Phần 04 là phần tiếp theo sau khi duyệt báo cáo</t>
+          <t>Thứ tự dependency đã thống nhất; PHẦN 05 đang mở lại theo quyết định custom ngày 09/10/2026</t>
         </is>
       </c>
     </row>
@@ -11148,12 +11180,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>NEXT</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Triển khai sau khi chốt workbook</t>
+          <t>Đã bàn giao</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11175,17 +11207,17 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>NOT_STARTED</t>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Sau 04</t>
+          <t>Đã đồng bộ contract 09/10</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Draft/submit</t>
+          <t>Description 4.000 từ, imageUrls[], migration legacy, draft/submit</t>
         </is>
       </c>
     </row>
@@ -11202,12 +11234,12 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>NOT_STARTED</t>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Trước review/timer</t>
+          <t>Chờ review/MySQL/BPMN cutover</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11229,12 +11261,12 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>NOT_STARTED</t>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Sau 04-06</t>
+          <t>Chờ review/MySQL/BPMN cutover</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -11433,7 +11465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11700,8 +11732,35 @@
         </is>
       </c>
     </row>
+    <row r="13" ht="42" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>D09</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Custom draft</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Description bắt buộc tối đa 4.000 từ; imageUrls là List&lt;String&gt; HTTP/HTTPS có thể rỗng; không fetch URL trong transaction.</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>ĐÃ TRIỂN KHAI 09/10/2026</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>Cột legacy giữ tên, nâng LONGTEXT; converter đọc JSON/raw/null</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:E12"/>
+  <autoFilter ref="A4:E13"/>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
@@ -11728,7 +11787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11886,181 +11945,247 @@
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>T07-01</t>
+          <t>T05-01</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Assignment race</t>
+          <t>Custom description</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Hai staff/manager đồng thời</t>
+          <t>Đúng 4.000 từ và 4.001 từ</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Một active assignment thắng</t>
+          <t>4.000 hợp lệ; 4.001 validation error, không ghi dữ liệu</t>
         </is>
       </c>
     </row>
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>T08-01</t>
+          <t>T05-02</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Chat access</t>
+          <t>Custom images</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Manager hoặc staff không phụ trách</t>
+          <t>List rỗng, nhiều URL HTTP(S), URL relative/sai scheme</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>403 và không subscribe WS</t>
+          <t>List hợp lệ giữ thứ tự; URL sai bị từ chối</t>
         </is>
       </c>
     </row>
     <row r="12" ht="42" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>T08-02</t>
+          <t>T05-03</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Timer race</t>
+          <t>Custom snapshot</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Submit form và timeout đồng thời</t>
+          <t>Sửa draft sau submit</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Chỉ một kết quả commit</t>
+          <t>OrderItem description/imageUrls không thay đổi</t>
         </is>
       </c>
     </row>
     <row r="13" ht="42" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>T09-01</t>
+          <t>T07-01</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Webhook duplicate</t>
+          <t>Assignment race</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Provider gửi lại callback</t>
+          <t>Hai staff/manager đồng thời</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>PAID/event đúng một lần theo milestone</t>
+          <t>Một active assignment thắng</t>
         </is>
       </c>
     </row>
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>T09-02</t>
+          <t>T08-01</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Webhook late</t>
+          <t>Chat access</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Callback sau timeout/cancel</t>
+          <t>Manager hoặc staff không phụ trách</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Không hồi sinh Order; reconciliationRequired</t>
+          <t>403 và không subscribe WS</t>
         </is>
       </c>
     </row>
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>T10-01</t>
+          <t>T08-02</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Checkpoint 1</t>
+          <t>Timer race</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Staff gửi ảnh</t>
+          <t>Submit form và timeout đồng thời</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>Mail tiến trình + notification; không manager review/status change</t>
+          <t>Chỉ một kết quả commit</t>
         </is>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>T10-02</t>
+          <t>T09-01</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Checkpoint 2</t>
+          <t>Webhook duplicate</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Mọi loại pass</t>
+          <t>Provider gửi lại callback</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>READY_TO_SHIP + release assignment cùng transaction</t>
+          <t>PAID/event đúng một lần theo milestone</t>
         </is>
       </c>
     </row>
     <row r="17" ht="42" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
+          <t>T09-02</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Webhook late</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Callback sau timeout/cancel</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Không hồi sinh Order; reconciliationRequired</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>T10-01</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Checkpoint 1</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Staff gửi ảnh</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Mail tiến trình + notification; không manager review/status change</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>T10-02</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Checkpoint 2</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Mọi loại pass</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>READY_TO_SHIP + release assignment cùng transaction</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
           <t>T12-01</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Guest access</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>Chỉ orderId, thiếu/sai token</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>401/403/429 phù hợp; không lộ dữ liệu</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:D17"/>
+  <autoFilter ref="A4:D20"/>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
@@ -12409,7 +12534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H94"/>
+  <dimension ref="A1:H95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -15946,7 +16071,7 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>OrderAgreementMapper.java</t>
+          <t>CustomRequestSubmissionMapper.java</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
@@ -15961,7 +16086,7 @@
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>05</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
@@ -15971,7 +16096,7 @@
       </c>
       <c r="G91" s="6" t="inlineStr">
         <is>
-          <t>Map agreement/version.</t>
+          <t>Map Order custom + draftId sang response submit chuyên biệt.</t>
         </is>
       </c>
       <c r="H91" s="6" t="inlineStr"/>
@@ -15984,7 +16109,7 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>PaymentAttemptMapper.java</t>
+          <t>OrderAgreementMapper.java</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
@@ -15999,7 +16124,7 @@
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>08</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr">
@@ -16009,7 +16134,7 @@
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
-          <t>Ẩn provider payload nhạy cảm.</t>
+          <t>Map agreement/version.</t>
         </is>
       </c>
       <c r="H92" s="5" t="inlineStr"/>
@@ -16022,7 +16147,7 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>ProductionCheckpointMapper.java</t>
+          <t>PaymentAttemptMapper.java</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
@@ -16037,7 +16162,7 @@
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>09</t>
         </is>
       </c>
       <c r="F93" s="6" t="inlineStr">
@@ -16047,7 +16172,7 @@
       </c>
       <c r="G93" s="6" t="inlineStr">
         <is>
-          <t>Map checkpoint, ảnh, decision.</t>
+          <t>Ẩn provider payload nhạy cảm.</t>
         </is>
       </c>
       <c r="H93" s="6" t="inlineStr"/>
@@ -16060,38 +16185,76 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
+          <t>ProductionCheckpointMapper.java</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>mapper</t>
+        </is>
+      </c>
+      <c r="D94" s="11" t="inlineStr">
+        <is>
+          <t>TẠO MỚI</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F94" s="5" t="inlineStr">
+        <is>
+          <t>Theo phạm vi</t>
+        </is>
+      </c>
+      <c r="G94" s="5" t="inlineStr">
+        <is>
+          <t>Map checkpoint, ảnh, decision.</t>
+        </is>
+      </c>
+      <c r="H94" s="5" t="inlineStr"/>
+    </row>
+    <row r="95" ht="42" customHeight="1">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>Mapper</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
           <t>OrderReceiptMapper.java</t>
         </is>
       </c>
-      <c r="C94" s="5" t="inlineStr">
+      <c r="C95" s="6" t="inlineStr">
         <is>
           <t>mapper</t>
         </is>
       </c>
-      <c r="D94" s="11" t="inlineStr">
+      <c r="D95" s="11" t="inlineStr">
         <is>
           <t>TẠO MỚI</t>
         </is>
       </c>
-      <c r="E94" s="5" t="inlineStr">
+      <c r="E95" s="6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="F94" s="5" t="inlineStr">
+      <c r="F95" s="6" t="inlineStr">
         <is>
           <t>Theo phạm vi</t>
         </is>
       </c>
-      <c r="G94" s="5" t="inlineStr">
+      <c r="G95" s="6" t="inlineStr">
         <is>
           <t>Map receipt/mismatch.</t>
         </is>
       </c>
-      <c r="H94" s="5" t="inlineStr"/>
+      <c r="H95" s="6" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H94"/>
+  <autoFilter ref="A4:H95"/>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
@@ -18236,7 +18399,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>TEXT/JSON</t>
+          <t>LONGTEXT/JSON</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -18251,7 +18414,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Thông số catalog/custom</t>
+          <t>Custom giữ description + imageUrls; catalog giữ thông số snapshot</t>
         </is>
       </c>
     </row>
@@ -18591,7 +18754,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -18631,7 +18794,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>DRAFT/SUBMITTED/...</t>
+          <t>DRAFT/SUBMITTED</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -18646,12 +18809,12 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>name/description/spec</t>
+          <t>description</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>String/TEXT</t>
+          <t>String/LONGTEXT</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -18661,12 +18824,12 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>validated</t>
+          <t>1..4.000 từ</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Thông tin custom</t>
+          <t>Mô tả sản phẩm custom</t>
         </is>
       </c>
     </row>
@@ -18706,27 +18869,27 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>attachments</t>
+          <t>imageUrls</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>JSON/ref</t>
+          <t>List&lt;String&gt;/JSON</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>safe URLs</t>
+          <t>list có thể rỗng; URL HTTP(S)</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Ảnh yêu cầu</t>
+          <t>Ảnh minh họa, không fetch server-side</t>
         </is>
       </c>
     </row>

--- a/docs/THIET_KE_CODE_VA_ENDPOINT.xlsx
+++ b/docs/THIET_KE_CODE_VA_ENDPOINT.xlsx
@@ -55,8 +55,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'10_CAMUNDA_EVENT'!$A$16:$F$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'11_WF_MAPPING'!$A$4:$G$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'12_KE_HOACH'!$A$4:$E$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'13_QUYET_DINH'!$A$4:$E$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'14_KIEM_THU'!$A$4:$D$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'13_QUYET_DINH'!$A$4:$E$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'14_KIEM_THU'!$A$4:$D$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -547,8 +547,8 @@
 </file>
 
 <file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="24" name="T_13_QUYET_DINH" displayName="T_13_QUYET_DINH" ref="A4:E13" headerRowCount="1">
-  <autoFilter ref="A4:E13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="24" name="T_13_QUYET_DINH" displayName="T_13_QUYET_DINH" ref="A4:E14" headerRowCount="1">
+  <autoFilter ref="A4:E14"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Mã"/>
     <tableColumn id="2" name="Chủ đề"/>
@@ -561,8 +561,8 @@
 </file>
 
 <file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="25" name="T_14_KIEM_THU" displayName="T_14_KIEM_THU" ref="A4:D20" headerRowCount="1">
-  <autoFilter ref="A4:D20"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="25" name="T_14_KIEM_THU" displayName="T_14_KIEM_THU" ref="A4:D21" headerRowCount="1">
+  <autoFilter ref="A4:D21"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Mã"/>
     <tableColumn id="2" name="Nhóm"/>
@@ -4362,7 +4362,7 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>Quản lý catalog, madeDay và availability.</t>
+          <t>Quản lý mẫu catalog, madeDay và availability nhận Order mới; không quản lý tồn thành phẩm.</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
@@ -7209,7 +7209,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>Thêm variant ACCEPTING_ORDERS và quantity dương.</t>
+          <t>Thêm mẫu variant ACCEPTING_ORDERS và quantity dương; availability không phải stock.</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -10266,22 +10266,22 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Legacy</t>
+          <t>WF02</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Không tạo lifecycle cạnh tranh</t>
+          <t>Guest manager review rồi luôn chờ assignment</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Guest dùng cùng lifecycle Order</t>
+          <t>Bỏ hasHandmadeItems/nhánh hàng làm sẵn; mọi CATALOG đều made-to-order</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Kế hoạch instance migration</t>
+          <t>Tương thích process instance cũ</t>
         </is>
       </c>
     </row>
@@ -11055,7 +11055,7 @@
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thứ tự dependency đã thống nhất; PHẦN 05 đang mở lại theo quyết định custom ngày 09/10/2026</t>
+          <t>Thứ tự dependency đã thống nhất; PHẦN 07 đang hiệu chỉnh để loại bỏ nhánh hàng làm sẵn legacy</t>
         </is>
       </c>
     </row>
@@ -11261,17 +11261,17 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>IMPLEMENTED</t>
+          <t>IN_PROGRESS</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Chờ review/MySQL/BPMN cutover</t>
+          <t>Còn bỏ gateway hasHandmadeItems của Guest BPMN</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>WF02</t>
+          <t>Guest CATALOG luôn chờ assignment</t>
         </is>
       </c>
     </row>
@@ -11465,7 +11465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11759,8 +11759,35 @@
         </is>
       </c>
     </row>
+    <row r="14" ht="42" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>D10</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Made-to-order và số loại item</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>CATALOG và CUSTOM đều handmade, không có hàng làm sẵn. CUSTOM đúng một OrderItem nhưng quantity có thể lớn; CATALOG có thể nhiều OrderItem, mỗi item có quantity riêng.</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT 09/10/2026</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Bỏ hasHandmadeItems/NOT_REQUIRED khỏi logic mới; availability chỉ kiểm soát nhận Order mới</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:E13"/>
+  <autoFilter ref="A4:E14"/>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
@@ -11787,7 +11814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12033,159 +12060,181 @@
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>T08-01</t>
+          <t>T07-02</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Chat access</t>
+          <t>Guest made-to-order</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Manager hoặc staff không phụ trách</t>
+          <t>Catalog item mang handmade=false legacy</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>403 và không subscribe WS</t>
+          <t>Vẫn chờ assignment; field legacy không được bỏ qua sản xuất</t>
         </is>
       </c>
     </row>
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>T08-02</t>
+          <t>T08-01</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Timer race</t>
+          <t>Chat access</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Submit form và timeout đồng thời</t>
+          <t>Manager hoặc staff không phụ trách</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>Chỉ một kết quả commit</t>
+          <t>403 và không subscribe WS</t>
         </is>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>T09-01</t>
+          <t>T08-02</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Webhook duplicate</t>
+          <t>Timer race</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Provider gửi lại callback</t>
+          <t>Submit form và timeout đồng thời</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>PAID/event đúng một lần theo milestone</t>
+          <t>Chỉ một kết quả commit</t>
         </is>
       </c>
     </row>
     <row r="17" ht="42" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>T09-02</t>
+          <t>T09-01</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Webhook late</t>
+          <t>Webhook duplicate</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Callback sau timeout/cancel</t>
+          <t>Provider gửi lại callback</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>Không hồi sinh Order; reconciliationRequired</t>
+          <t>PAID/event đúng một lần theo milestone</t>
         </is>
       </c>
     </row>
     <row r="18" ht="42" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>T10-01</t>
+          <t>T09-02</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Checkpoint 1</t>
+          <t>Webhook late</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Staff gửi ảnh</t>
+          <t>Callback sau timeout/cancel</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Mail tiến trình + notification; không manager review/status change</t>
+          <t>Không hồi sinh Order; reconciliationRequired</t>
         </is>
       </c>
     </row>
     <row r="19" ht="42" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>T10-02</t>
+          <t>T10-01</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Checkpoint 2</t>
+          <t>Checkpoint 1</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Mọi loại pass</t>
+          <t>Staff gửi ảnh</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>READY_TO_SHIP + release assignment cùng transaction</t>
+          <t>Mail tiến trình + notification; không manager review/status change</t>
         </is>
       </c>
     </row>
     <row r="20" ht="42" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
+          <t>T10-02</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Checkpoint 2</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Mọi loại pass</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>READY_TO_SHIP + release assignment cùng transaction</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
           <t>T12-01</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>Guest access</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>Chỉ orderId, thiếu/sai token</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>401/403/429 phù hợp; không lộ dữ liệu</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:D20"/>
+  <autoFilter ref="A4:D21"/>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
@@ -12678,7 +12727,7 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>Dòng hàng; lưu snapshot catalog/custom, đơn giá nullable, quantity và thời lượng sản xuất.</t>
+          <t>Dòng hàng made-to-order; CATALOG có thể nhiều item, CUSTOM đúng một item; mỗi item có quantity riêng, snapshot và thời lượng sản xuất.</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
@@ -13266,7 +13315,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Mẫu catalog, availability và madeDay do manager nhập, madeDay &gt;= 2.</t>
+          <t>Mẫu thiết kế catalog made-to-order; availability chỉ bật/tắt nhận Order mới, madeDay do manager nhập và &gt;= 2.</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -14446,7 +14495,7 @@
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>Quản lý catalog, madeDay và availability.</t>
+          <t>Quản lý mẫu catalog, madeDay và availability nhận Order mới; không quản lý tồn thành phẩm.</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
@@ -16425,7 +16474,7 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>Dòng hàng; lưu snapshot catalog/custom, đơn giá nullable, quantity và thời lượng sản xuất.</t>
+          <t>Dòng hàng made-to-order; CATALOG có thể nhiều item, CUSTOM đúng một item; mỗi item có quantity riêng, snapshot và thời lượng sản xuất.</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
@@ -17013,7 +17062,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Mẫu catalog, availability và madeDay do manager nhập, madeDay &gt;= 2.</t>
+          <t>Mẫu thiết kế catalog made-to-order; availability chỉ bật/tắt nhận Order mới, madeDay do manager nhập và &gt;= 2.</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
